--- a/InputData/elec/BTaDLP/BAU Trans and Distr Loss Perc.xlsx
+++ b/InputData/elec/BTaDLP/BAU Trans and Distr Loss Perc.xlsx
@@ -1,14 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BTaDLP/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31500957-0091-E24C-A07B-E9AD9C675CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="About" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="6.4.5 HEESI" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="BTaDLP" sheetId="3" r:id="rId6"/>
+    <sheet name="About" sheetId="1" r:id="rId1"/>
+    <sheet name="6.4.5 HEESI" sheetId="2" r:id="rId2"/>
+    <sheet name="BTaDLP" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -63,34 +85,46 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
-    <font/>
     <font>
-      <sz val="11.0"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -98,7 +132,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -108,7 +142,13 @@
     </fill>
   </fills>
   <borders count="5">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -122,27 +162,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -152,54 +199,56 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -216,7 +265,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr lang="en-US" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -229,9 +278,11 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -239,6 +290,12 @@
           <c:tx>
             <c:strRef>
               <c:f>'6.4.5 HEESI'!$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Transmission &amp; Distribution Losses (%)</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -252,18 +309,105 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'6.4.5 HEESI'!$A$5:$A$15</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2019</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'6.4.5 HEESI'!$F$5:$F$15</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>9.93</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.2100000000000009</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.0500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.8699999999999992</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.5500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.35</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0058-6A47-815C-BA32C655AAD9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
         <c:axId val="188008295"/>
         <c:axId val="317442097"/>
       </c:lineChart>
@@ -289,7 +433,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0">
+                  <a:rPr lang="en-US" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -305,7 +449,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -318,9 +462,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="317442097"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="317442097"/>
@@ -364,7 +514,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0">
+                  <a:rPr lang="en-US" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -396,9 +546,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="188008295"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -416,20 +569,24 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -438,9 +595,15 @@
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1" title="Chart"/>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -449,7 +612,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -458,12 +621,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -653,17 +812,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,59 +833,60 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A6"/>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="11.13"/>
-    <col customWidth="1" min="3" max="3" width="12.63"/>
-    <col customWidth="1" min="4" max="4" width="9.88"/>
-    <col customWidth="1" min="5" max="5" width="9.0"/>
-    <col customWidth="1" min="6" max="6" width="12.38"/>
+    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -763,9 +926,9 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7">
-        <v>2009.0</v>
+        <v>2009</v>
       </c>
       <c r="B5" s="7">
         <v>29.95</v>
@@ -777,15 +940,15 @@
         <v>76.37</v>
       </c>
       <c r="E5" s="7">
-        <v>23438.0</v>
+        <v>23438</v>
       </c>
       <c r="F5" s="7">
         <v>9.93</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8">
-        <f t="shared" ref="A6:A15" si="1">A5+1</f>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7">
+        <f t="shared" ref="A6:A15" si="0">A5+1</f>
         <v>2010</v>
       </c>
       <c r="B6" s="7">
@@ -798,15 +961,15 @@
         <v>77.78</v>
       </c>
       <c r="E6" s="7">
-        <v>24917.0</v>
+        <v>24917</v>
       </c>
       <c r="F6" s="7">
-        <v>9.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8">
-        <f t="shared" si="1"/>
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7">
+        <f t="shared" si="0"/>
         <v>2011</v>
       </c>
       <c r="B7" s="7">
@@ -819,15 +982,15 @@
         <v>78.53</v>
       </c>
       <c r="E7" s="7">
-        <v>26665.0</v>
+        <v>26665</v>
       </c>
       <c r="F7" s="7">
         <v>9.41</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8">
-        <f t="shared" si="1"/>
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7">
+        <f t="shared" si="0"/>
         <v>2012</v>
       </c>
       <c r="B8" s="7">
@@ -837,18 +1000,18 @@
         <v>51.96</v>
       </c>
       <c r="D8" s="7">
-        <v>79.18</v>
+        <v>79.180000000000007</v>
       </c>
       <c r="E8" s="7">
-        <v>28882.0</v>
+        <v>28882</v>
       </c>
       <c r="F8" s="7">
-        <v>9.21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8">
-        <f t="shared" si="1"/>
+        <v>9.2100000000000009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7">
+        <f t="shared" si="0"/>
         <v>2013</v>
       </c>
       <c r="B9" s="7">
@@ -858,18 +1021,18 @@
         <v>54.72</v>
       </c>
       <c r="D9" s="7">
-        <v>80.04</v>
+        <v>80.040000000000006</v>
       </c>
       <c r="E9" s="7">
-        <v>30834.0</v>
+        <v>30834</v>
       </c>
       <c r="F9" s="7">
-        <v>9.05</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8">
-        <f t="shared" si="1"/>
+        <v>9.0500000000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7">
+        <f t="shared" si="0"/>
         <v>2014</v>
       </c>
       <c r="B10" s="7">
@@ -879,18 +1042,18 @@
         <v>50.94</v>
       </c>
       <c r="D10" s="7">
-        <v>78.26</v>
+        <v>78.260000000000005</v>
       </c>
       <c r="E10" s="7">
-        <v>33321.0</v>
+        <v>33321</v>
       </c>
       <c r="F10" s="7">
         <v>8.98</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8">
-        <f t="shared" si="1"/>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7">
+        <f t="shared" si="0"/>
         <v>2015</v>
       </c>
       <c r="B11" s="7">
@@ -903,15 +1066,15 @@
         <v>80.02</v>
       </c>
       <c r="E11" s="7">
-        <v>33381.0</v>
+        <v>33381</v>
       </c>
       <c r="F11" s="7">
-        <v>8.87</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8">
-        <f t="shared" si="1"/>
+        <v>8.8699999999999992</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7">
+        <f t="shared" si="0"/>
         <v>2016</v>
       </c>
       <c r="B12" s="7">
@@ -924,15 +1087,15 @@
         <v>62.62</v>
       </c>
       <c r="E12" s="7">
-        <v>32304.0</v>
+        <v>32304</v>
       </c>
       <c r="F12" s="7">
-        <v>8.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8">
-        <f t="shared" si="1"/>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7">
+        <f t="shared" si="0"/>
         <v>2017</v>
       </c>
       <c r="B13" s="7">
@@ -942,18 +1105,18 @@
         <v>51.98</v>
       </c>
       <c r="D13" s="7">
-        <v>74.93</v>
+        <v>74.930000000000007</v>
       </c>
       <c r="E13" s="7">
-        <v>38797.0</v>
+        <v>38797</v>
       </c>
       <c r="F13" s="7">
         <v>9.75</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8">
-        <f t="shared" si="1"/>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7">
+        <f t="shared" si="0"/>
         <v>2018</v>
       </c>
       <c r="B14" s="7">
@@ -963,18 +1126,18 @@
         <v>52.73</v>
       </c>
       <c r="D14" s="7">
-        <v>75.76</v>
+        <v>75.760000000000005</v>
       </c>
       <c r="E14" s="7">
-        <v>37944.0</v>
+        <v>37944</v>
       </c>
       <c r="F14" s="7">
-        <v>9.55</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8">
-        <f t="shared" si="1"/>
+        <v>9.5500000000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7">
+        <f t="shared" si="0"/>
         <v>2019</v>
       </c>
       <c r="B15" s="7">
@@ -987,295 +1150,438 @@
         <v>76.41</v>
       </c>
       <c r="E15" s="7">
-        <v>41671.0</v>
+        <v>41671</v>
       </c>
       <c r="F15" s="7">
         <v>9.35</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12">
-        <f>average(F5:F15)</f>
-        <v>9.318181818</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="8">
+        <f>AVERAGE(F5:F15)</f>
+        <v>9.3181818181818183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="9"/>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="10">
         <f>9.32/100</f>
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A16:E16"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0B5394"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:BB2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.5"/>
+    <col min="1" max="1" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="3">
-        <v>2019.0</v>
-      </c>
-      <c r="C1" s="13">
-        <f t="shared" ref="C1:AG1" si="1">B1+1</f>
+        <v>2019</v>
+      </c>
+      <c r="C1" s="3">
+        <f t="shared" ref="C1:AG1" si="0">B1+1</f>
         <v>2020</v>
       </c>
-      <c r="D1" s="13">
-        <f t="shared" si="1"/>
+      <c r="D1" s="3">
+        <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="E1" s="13">
-        <f t="shared" si="1"/>
+      <c r="E1" s="3">
+        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="F1" s="13">
-        <f t="shared" si="1"/>
+      <c r="F1" s="3">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="G1" s="13">
-        <f t="shared" si="1"/>
+      <c r="G1" s="3">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="H1" s="13">
-        <f t="shared" si="1"/>
+      <c r="H1" s="3">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="I1" s="13">
-        <f t="shared" si="1"/>
+      <c r="I1" s="3">
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="J1" s="13">
-        <f t="shared" si="1"/>
+      <c r="J1" s="3">
+        <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="K1" s="13">
-        <f t="shared" si="1"/>
+      <c r="K1" s="3">
+        <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="L1" s="13">
-        <f t="shared" si="1"/>
+      <c r="L1" s="3">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="M1" s="13">
-        <f t="shared" si="1"/>
+      <c r="M1" s="3">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="N1" s="13">
-        <f t="shared" si="1"/>
+      <c r="N1" s="3">
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="O1" s="13">
-        <f t="shared" si="1"/>
+      <c r="O1" s="3">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="P1" s="13">
-        <f t="shared" si="1"/>
+      <c r="P1" s="3">
+        <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="Q1" s="13">
-        <f t="shared" si="1"/>
+      <c r="Q1" s="3">
+        <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="R1" s="13">
-        <f t="shared" si="1"/>
+      <c r="R1" s="3">
+        <f t="shared" si="0"/>
         <v>2035</v>
       </c>
-      <c r="S1" s="13">
-        <f t="shared" si="1"/>
+      <c r="S1" s="3">
+        <f t="shared" si="0"/>
         <v>2036</v>
       </c>
-      <c r="T1" s="13">
-        <f t="shared" si="1"/>
+      <c r="T1" s="3">
+        <f t="shared" si="0"/>
         <v>2037</v>
       </c>
-      <c r="U1" s="13">
-        <f t="shared" si="1"/>
+      <c r="U1" s="3">
+        <f t="shared" si="0"/>
         <v>2038</v>
       </c>
-      <c r="V1" s="13">
-        <f t="shared" si="1"/>
+      <c r="V1" s="3">
+        <f t="shared" si="0"/>
         <v>2039</v>
       </c>
-      <c r="W1" s="13">
-        <f t="shared" si="1"/>
+      <c r="W1" s="3">
+        <f t="shared" si="0"/>
         <v>2040</v>
       </c>
-      <c r="X1" s="13">
-        <f t="shared" si="1"/>
+      <c r="X1" s="3">
+        <f t="shared" si="0"/>
         <v>2041</v>
       </c>
-      <c r="Y1" s="13">
-        <f t="shared" si="1"/>
+      <c r="Y1" s="3">
+        <f t="shared" si="0"/>
         <v>2042</v>
       </c>
-      <c r="Z1" s="13">
-        <f t="shared" si="1"/>
+      <c r="Z1" s="3">
+        <f t="shared" si="0"/>
         <v>2043</v>
       </c>
-      <c r="AA1" s="13">
-        <f t="shared" si="1"/>
+      <c r="AA1" s="3">
+        <f t="shared" si="0"/>
         <v>2044</v>
       </c>
-      <c r="AB1" s="13">
-        <f t="shared" si="1"/>
+      <c r="AB1" s="3">
+        <f t="shared" si="0"/>
         <v>2045</v>
       </c>
-      <c r="AC1" s="13">
-        <f t="shared" si="1"/>
+      <c r="AC1" s="3">
+        <f t="shared" si="0"/>
         <v>2046</v>
       </c>
-      <c r="AD1" s="13">
-        <f t="shared" si="1"/>
+      <c r="AD1" s="3">
+        <f t="shared" si="0"/>
         <v>2047</v>
       </c>
-      <c r="AE1" s="13">
-        <f t="shared" si="1"/>
+      <c r="AE1" s="3">
+        <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="AF1" s="13">
-        <f t="shared" si="1"/>
+      <c r="AF1" s="3">
+        <f t="shared" si="0"/>
         <v>2049</v>
       </c>
-      <c r="AG1" s="13">
-        <f t="shared" si="1"/>
+      <c r="AG1" s="3">
+        <f t="shared" si="0"/>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="AH1" s="3">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="3">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="3">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="3">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="3">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="3">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="3">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="3">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="3">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="3">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="3">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="3">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="3">
+        <v>2070</v>
+      </c>
+      <c r="BB1" s="3"/>
+    </row>
+    <row r="2" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="C2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="D2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="E2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="F2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="G2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="H2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="I2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="J2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="K2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="L2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="M2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="N2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="O2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="P2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="R2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="S2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="T2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="U2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="V2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="W2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="X2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="Y2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="Z2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AA2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AB2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AC2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AD2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AE2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AF2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AH2">
+        <f>AG2</f>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" ref="AI2:BA2" si="1">AH2</f>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="1"/>
+        <v>9.3200000000000005E-2</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>